--- a/tests/fixtures/corporate.xlsx
+++ b/tests/fixtures/corporate.xlsx
@@ -17,13 +17,20 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <u val="singleAccounting"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,10 +443,10 @@
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>1204000</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>46023</v>
       </c>
       <c r="D2">
@@ -469,10 +479,10 @@
           <t>APAC</t>
         </is>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>987500</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>46031</v>
       </c>
       <c r="D3">
@@ -480,6 +490,11 @@
       </c>
       <c r="E3">
         <v>2</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Superseded total</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -488,10 +503,10 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>1410250</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>46038</v>
       </c>
       <c r="D4">
@@ -507,10 +522,10 @@
           <t>LATAM</t>
         </is>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>412000</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>46045</v>
       </c>
       <c r="D5">
